--- a/ig/test-tabs-svs/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
+++ b/ig/test-tabs-svs/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="1105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="1127">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260601120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -735,12 +735,6 @@
     <t>Urgences Médico-Psychologiques (CUMP)</t>
   </si>
   <si>
-    <t>148</t>
-  </si>
-  <si>
-    <t>Urgences spécialisées cardiologiques</t>
-  </si>
-  <si>
     <t>152</t>
   </si>
   <si>
@@ -1728,7 +1722,7 @@
     <t>334</t>
   </si>
   <si>
-    <t>Activité de prévention</t>
+    <t>Activité de dépistage et de prévention</t>
   </si>
   <si>
     <t>335</t>
@@ -1932,13 +1926,13 @@
     <t>369</t>
   </si>
   <si>
-    <t>Soins intensifs spécialisés néonatalogique</t>
+    <t>Soins intensifs spécialisés néonatalogie</t>
   </si>
   <si>
     <t>370</t>
   </si>
   <si>
-    <t>Soins intensifs spécialisés pédiatrique</t>
+    <t>Soins intensifs spécialisés pédiatrie</t>
   </si>
   <si>
     <t>371</t>
@@ -3319,6 +3313,78 @@
   </si>
   <si>
     <t>Soins infirmiers en pratique avancée en santé mentale</t>
+  </si>
+  <si>
+    <t>618</t>
+  </si>
+  <si>
+    <t>Collecte de don de lait maternel cru</t>
+  </si>
+  <si>
+    <t>619</t>
+  </si>
+  <si>
+    <t>Distribution de lait maternel pasteurisé</t>
+  </si>
+  <si>
+    <t>620</t>
+  </si>
+  <si>
+    <t>Bilan psychomoteur</t>
+  </si>
+  <si>
+    <t>621</t>
+  </si>
+  <si>
+    <t>Soin psychomoteur</t>
+  </si>
+  <si>
+    <t>622</t>
+  </si>
+  <si>
+    <t>Education psychomotrice (pédagogie du développement psychomoteur)</t>
+  </si>
+  <si>
+    <t>623</t>
+  </si>
+  <si>
+    <t>Stimulation psychomotrice (stimulation du fonctionnement psychomoteur à visée préventive)</t>
+  </si>
+  <si>
+    <t>624</t>
+  </si>
+  <si>
+    <t>Rééducation de la graphomotricité et de l’écriture (dysgraphie)</t>
+  </si>
+  <si>
+    <t>625</t>
+  </si>
+  <si>
+    <t>Orthoptie : orientation troubles neuro-visuels (pathologies neurologiques, maladies neurodégénératives)</t>
+  </si>
+  <si>
+    <t>626</t>
+  </si>
+  <si>
+    <t>Orthoptie orientation basse vision</t>
+  </si>
+  <si>
+    <t>627</t>
+  </si>
+  <si>
+    <t>Orthoptie orientation pédiatrique</t>
+  </si>
+  <si>
+    <t>628</t>
+  </si>
+  <si>
+    <t>Dispensation de médicaments et autres produits de santé appartenant au monopole pharmaceutique</t>
+  </si>
+  <si>
+    <t>629</t>
+  </si>
+  <si>
+    <t>Conseil et accompagnement dans la gestion des traitements</t>
   </si>
   <si>
     <t/>
@@ -3589,7 +3655,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B540"/>
+  <dimension ref="A1:B551"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -7905,15 +7971,103 @@
         <v>1102</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B540" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="s" s="2">
+        <v>1106</v>
+      </c>
+      <c r="B541" t="s" s="2">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="s" s="2">
+        <v>1108</v>
+      </c>
+      <c r="B542" t="s" s="2">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="s" s="2">
+        <v>1110</v>
+      </c>
+      <c r="B543" t="s" s="2">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="s" s="2">
+        <v>1112</v>
+      </c>
+      <c r="B544" t="s" s="2">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="s" s="2">
+        <v>1114</v>
+      </c>
+      <c r="B545" t="s" s="2">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="s" s="2">
+        <v>1116</v>
+      </c>
+      <c r="B546" t="s" s="2">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="s" s="2">
+        <v>1118</v>
+      </c>
+      <c r="B547" t="s" s="2">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="s" s="2">
+        <v>1120</v>
+      </c>
+      <c r="B548" t="s" s="2">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="s" s="2">
+        <v>1122</v>
+      </c>
+      <c r="B549" t="s" s="2">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="s" s="2">
+        <v>1124</v>
+      </c>
+      <c r="B550" t="s" s="2">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="s" s="2">
+        <v>1125</v>
+      </c>
+      <c r="B551" t="s" s="2">
+        <v>1126</v>
       </c>
     </row>
   </sheetData>
